--- a/data/3.meta_data/basic_info/25_01_31_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/25_01_31_basic_info.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>review</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>review</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
